--- a/output/palmer_drought_trendlines/state/Decade.xlsx
+++ b/output/palmer_drought_trendlines/state/Decade.xlsx
@@ -43,6 +43,9 @@
     <t>Trend Y</t>
   </si>
   <si>
+    <t>Arizona</t>
+  </si>
+  <si>
     <t>New Mexico</t>
   </si>
   <si>
@@ -52,136 +55,133 @@
     <t>Wyoming</t>
   </si>
   <si>
-    <t>Arizona</t>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Colorado</t>
   </si>
   <si>
     <t>Montana</t>
   </si>
   <si>
-    <t>Nevada</t>
-  </si>
-  <si>
-    <t>Colorado</t>
-  </si>
-  <si>
-    <t>California</t>
-  </si>
-  <si>
     <t>Florida</t>
   </si>
   <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
     <t>Oregon</t>
   </si>
   <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
     <t>Idaho</t>
   </si>
   <si>
-    <t>Delaware</t>
-  </si>
-  <si>
-    <t>New Jersey</t>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Georgia</t>
   </si>
   <si>
     <t>Connecticut</t>
   </si>
   <si>
-    <t>North Carolina</t>
+    <t>Washington</t>
   </si>
   <si>
     <t>Texas</t>
   </si>
   <si>
-    <t>Maryland</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>South Carolina</t>
-  </si>
-  <si>
-    <t>Washington</t>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
   <si>
     <t>Nebraska</t>
   </si>
   <si>
-    <t>North Dakota</t>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
   </si>
   <si>
     <t>Kansas</t>
   </si>
   <si>
-    <t>Virginia</t>
-  </si>
-  <si>
-    <t>West Virginia</t>
-  </si>
-  <si>
-    <t>Rhode Island</t>
-  </si>
-  <si>
-    <t>Massachusetts</t>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
   </si>
   <si>
     <t>Missouri</t>
   </si>
   <si>
-    <t>Pennsylvania</t>
-  </si>
-  <si>
-    <t>Arkansas</t>
-  </si>
-  <si>
-    <t>Minnesota</t>
+    <t>Ohio</t>
   </si>
   <si>
     <t>Louisiana</t>
   </si>
   <si>
-    <t>Ohio</t>
-  </si>
-  <si>
-    <t>South Dakota</t>
+    <t>Maine</t>
   </si>
   <si>
     <t>Alabama</t>
   </si>
   <si>
-    <t>Maine</t>
-  </si>
-  <si>
     <t>Oklahoma</t>
   </si>
   <si>
     <t>Mississippi</t>
   </si>
   <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
     <t>Illinois</t>
   </si>
   <si>
     <t>Wisconsin</t>
   </si>
   <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
-    <t>Tennessee</t>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Michigan</t>
   </si>
   <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>New York</t>
-  </si>
-  <si>
     <t>Indiana</t>
-  </si>
-  <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Kentucky</t>
   </si>
   <si>
     <t>Vermont</t>
@@ -576,176 +576,176 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.02017829742546101</v>
+        <v>-0.03508872538468063</v>
       </c>
       <c r="D2">
-        <v>1.175906342745697</v>
+        <v>1.731814127024507</v>
       </c>
       <c r="E2">
-        <v>-0.303621470035299</v>
+        <v>-0.3107506901762977</v>
       </c>
       <c r="F2">
-        <v>0.0004015054049191482</v>
+        <v>0.0002872831800671375</v>
       </c>
       <c r="G2">
-        <v>0.005553653794825718</v>
+        <v>0.009413086118596127</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-1.447272322564233</v>
+        <v>-2.829720172983975</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.01955481203694128</v>
+        <v>-0.03453208617889363</v>
       </c>
       <c r="D3">
-        <v>1.234294072755025</v>
+        <v>1.979958110743663</v>
       </c>
       <c r="E3">
-        <v>-0.2906437551731059</v>
+        <v>-0.2966509958676844</v>
       </c>
       <c r="F3">
-        <v>0.0007228328095723511</v>
+        <v>0.0005524815337706512</v>
       </c>
       <c r="G3">
-        <v>0.005646201382278454</v>
+        <v>0.009749948387324566</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-1.307831492047341</v>
+        <v>-2.50921309251251</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.01917962713958645</v>
+        <v>-0.03357054054230346</v>
       </c>
       <c r="D4">
-        <v>1.319558297295006</v>
+        <v>1.867318748410074</v>
       </c>
       <c r="E4">
-        <v>-0.2558782602921283</v>
+        <v>-0.2781409132969345</v>
       </c>
       <c r="F4">
-        <v>0.003063240802315445</v>
+        <v>0.001241512086501293</v>
       </c>
       <c r="G4">
-        <v>0.006355223996377302</v>
+        <v>0.01016804276084581</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-1.173793230851232</v>
+        <v>-2.496851522089376</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.01885052438445978</v>
+        <v>-0.03322352764677874</v>
       </c>
       <c r="D5">
-        <v>0.8866862969558219</v>
+        <v>1.897072670228102</v>
       </c>
       <c r="E5">
-        <v>-0.3074455730292511</v>
+        <v>-0.2669867485791529</v>
       </c>
       <c r="F5">
-        <v>0.0003358652699062882</v>
+        <v>0.001970481768307933</v>
       </c>
       <c r="G5">
-        <v>0.005117080864899213</v>
+        <v>0.01051783395301107</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-1.56388187302395</v>
+        <v>-2.421985923853134</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.01760987287112956</v>
+        <v>-0.03158592907135264</v>
       </c>
       <c r="D6">
-        <v>1.373095904350039</v>
+        <v>1.41894021877385</v>
       </c>
       <c r="E6">
-        <v>-0.2868478550422435</v>
+        <v>-0.2631578961771068</v>
       </c>
       <c r="F6">
-        <v>0.0008540730003803274</v>
+        <v>0.00229895020729626</v>
       </c>
       <c r="G6">
-        <v>0.005158074799522202</v>
+        <v>0.01015597472652152</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-0.9161875688968038</v>
+        <v>-2.687230560501993</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.01747651586944389</v>
+        <v>-0.03142366723414805</v>
       </c>
       <c r="D7">
-        <v>0.784837488340542</v>
+        <v>1.549571779869416</v>
       </c>
       <c r="E7">
-        <v>-0.2733626667909262</v>
+        <v>-0.3001135647157354</v>
       </c>
       <c r="F7">
-        <v>0.001516752768301513</v>
+        <v>0.0004719399738457462</v>
       </c>
       <c r="G7">
-        <v>0.00539360188555091</v>
+        <v>0.008759997828912363</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-1.487109574687164</v>
+        <v>-2.535504960569831</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -756,54 +756,54 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.01638181110418455</v>
+        <v>-0.02885326236554933</v>
       </c>
       <c r="D8">
-        <v>1.091110955651658</v>
+        <v>1.612464004070212</v>
       </c>
       <c r="E8">
-        <v>-0.2469535322823822</v>
+        <v>-0.2448724933694323</v>
       </c>
       <c r="F8">
-        <v>0.004308478237979549</v>
+        <v>0.004657312747706026</v>
       </c>
       <c r="G8">
-        <v>0.005637817560606562</v>
+        <v>0.01001972555005384</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-1.038524487892333</v>
+        <v>-2.138460103451201</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.0154230949072974</v>
+        <v>-0.0273257943108363</v>
       </c>
       <c r="D9">
-        <v>0.7055224709573478</v>
+        <v>1.80250758924786</v>
       </c>
       <c r="E9">
-        <v>-0.2922416526727816</v>
+        <v>-0.2555103739107908</v>
       </c>
       <c r="F9">
-        <v>0.0006733445571225555</v>
+        <v>0.003107341937854425</v>
       </c>
       <c r="G9">
-        <v>0.004426618630448584</v>
+        <v>0.009068429046441128</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.299479866991315</v>
+        <v>-1.749845671160859</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,373 +814,373 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.01121656691481164</v>
+        <v>-0.02221342126033045</v>
       </c>
       <c r="D10">
-        <v>0.550076570847113</v>
+        <v>1.087895700839481</v>
       </c>
       <c r="E10">
-        <v>-0.263754315831564</v>
+        <v>-0.2232554601689635</v>
       </c>
       <c r="F10">
-        <v>0.002244725321922833</v>
+        <v>0.01007696425709046</v>
       </c>
       <c r="G10">
-        <v>0.003597753526299296</v>
+        <v>0.008506274106862426</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-0.9080771280784002</v>
+        <v>-1.799849063003477</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.007667610046190564</v>
+        <v>-0.02066297347187707</v>
       </c>
       <c r="D11">
-        <v>0.2386372848299841</v>
+        <v>1.057205800050878</v>
       </c>
       <c r="E11">
-        <v>-0.1807793713671079</v>
+        <v>-0.2178627853954801</v>
       </c>
       <c r="F11">
-        <v>0.03804537143883543</v>
+        <v>0.01209140255286077</v>
       </c>
       <c r="G11">
-        <v>0.003658678835955125</v>
+        <v>0.008118555150468637</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-0.7581520211747891</v>
+        <v>-1.628980751293141</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.007085768890653149</v>
+        <v>-0.01742679294757647</v>
       </c>
       <c r="D12">
-        <v>0.2296709912660056</v>
+        <v>0.7239194437378111</v>
       </c>
       <c r="E12">
-        <v>-0.1472046832501807</v>
+        <v>-0.1834672648417183</v>
       </c>
       <c r="F12">
-        <v>0.09211288841321001</v>
+        <v>0.03522708457255905</v>
       </c>
       <c r="G12">
-        <v>0.004175769703321322</v>
+        <v>0.008189400934417949</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-0.6914789645189037</v>
+        <v>-1.54156363944713</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.004495301785469685</v>
+        <v>-0.01729513727178444</v>
       </c>
       <c r="D13">
-        <v>0.06536369032476919</v>
+        <v>0.627656406342746</v>
       </c>
       <c r="E13">
-        <v>-0.1128883084266106</v>
+        <v>-0.1791685741137918</v>
       </c>
       <c r="F13">
-        <v>0.1974760079249856</v>
+        <v>0.03982341166673574</v>
       </c>
       <c r="G13">
-        <v>0.003470189190677994</v>
+        <v>0.008329241140582491</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-0.5190255417862899</v>
+        <v>-1.620711438989231</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.00403928224323798</v>
+        <v>-0.01693982610283807</v>
       </c>
       <c r="D14">
-        <v>0.2465738149749852</v>
+        <v>0.7000193335029263</v>
       </c>
       <c r="E14">
-        <v>-0.1109043768413585</v>
+        <v>-0.1795768178720027</v>
       </c>
       <c r="F14">
-        <v>0.2055186405339849</v>
+        <v>0.03936631565967194</v>
       </c>
       <c r="G14">
-        <v>0.003174654103632271</v>
+        <v>0.008138963037474705</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-0.2785328766459522</v>
+        <v>-1.502158059866023</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.003820125787042603</v>
+        <v>-0.01648034361974836</v>
       </c>
       <c r="D15">
-        <v>0.1477910200966676</v>
+        <v>0.8478317646061231</v>
       </c>
       <c r="E15">
-        <v>-0.1048986895316032</v>
+        <v>-0.1771901715481343</v>
       </c>
       <c r="F15">
-        <v>0.2312921406652906</v>
+        <v>0.04210208207847842</v>
       </c>
       <c r="G15">
-        <v>0.003176385831935915</v>
+        <v>0.008028381600482176</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-0.3488253322188709</v>
+        <v>-1.294612905961164</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.003564618422364545</v>
+        <v>-0.01621008159990608</v>
       </c>
       <c r="D16">
-        <v>0.1214157127109304</v>
+        <v>0.5675743237513787</v>
       </c>
       <c r="E16">
-        <v>-0.09461503335178625</v>
+        <v>-0.1635863279376681</v>
       </c>
       <c r="F16">
-        <v>0.2805307671124722</v>
+        <v>0.06089818026672635</v>
       </c>
       <c r="G16">
-        <v>0.003289489981358912</v>
+        <v>0.008573859995359425</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-0.3419846821964605</v>
+        <v>-1.539736284236412</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.003322733033099356</v>
+        <v>-0.01521516936383383</v>
       </c>
       <c r="D17">
-        <v>-0.07735800898838266</v>
+        <v>0.6154857966590352</v>
       </c>
       <c r="E17">
-        <v>-0.05063899683806632</v>
+        <v>-0.1605092291234103</v>
       </c>
       <c r="F17">
-        <v>0.5641865073011356</v>
+        <v>0.06598726241507213</v>
       </c>
       <c r="G17">
-        <v>0.005747528475616043</v>
+        <v>0.008206110640579049</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-0.5093133032912989</v>
+        <v>-1.362486220639363</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.00310140272260598</v>
+        <v>-0.01458012771592014</v>
       </c>
       <c r="D18">
-        <v>0.02232866954973295</v>
+        <v>0.5133806495378619</v>
       </c>
       <c r="E18">
-        <v>-0.07958944718503759</v>
+        <v>-0.151535235476888</v>
       </c>
       <c r="F18">
-        <v>0.3643242669185092</v>
+        <v>0.08283308308976954</v>
       </c>
       <c r="G18">
-        <v>0.003406835072318522</v>
+        <v>0.008341257825409702</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-0.3808536843890445</v>
+        <v>-1.382035953531757</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.002744959293229455</v>
+        <v>-0.01394098585210262</v>
       </c>
       <c r="D19">
-        <v>0.04122763503773433</v>
+        <v>0.5611817179682869</v>
       </c>
       <c r="E19">
-        <v>-0.0611821513865568</v>
+        <v>-0.1536363360892627</v>
       </c>
       <c r="F19">
-        <v>0.4858672873514133</v>
+        <v>0.07860872593120999</v>
       </c>
       <c r="G19">
-        <v>0.003927580771757388</v>
+        <v>0.007863951692105393</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-0.3156170730820949</v>
+        <v>-1.251146442805054</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.002728301572081782</v>
+        <v>-0.01392460847047467</v>
       </c>
       <c r="D20">
-        <v>0.02331480539302988</v>
+        <v>0.518535402357331</v>
       </c>
       <c r="E20">
-        <v>-0.0665000636895592</v>
+        <v>-0.1505977418802818</v>
       </c>
       <c r="F20">
-        <v>0.4486905478083124</v>
+        <v>0.08477571512489022</v>
       </c>
       <c r="G20">
-        <v>0.003590345352666307</v>
+        <v>0.008016989610981563</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-0.3313643989776018</v>
+        <v>-1.291663698804376</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.002711204402313539</v>
+        <v>-0.01376410908687684</v>
       </c>
       <c r="D21">
-        <v>0.007786398711100068</v>
+        <v>0.3687024506062925</v>
       </c>
       <c r="E21">
-        <v>-0.07093131115195506</v>
+        <v>-0.1163552110858013</v>
       </c>
       <c r="F21">
-        <v>0.4189718089791773</v>
+        <v>0.183972567053515</v>
       </c>
       <c r="G21">
-        <v>0.003343931075072536</v>
+        <v>0.01030458850574281</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-0.34467017358966</v>
+        <v>-1.420631730687697</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.0008127337133315312</v>
+        <v>-0.01308104547025942</v>
       </c>
       <c r="D22">
-        <v>0.6543000084796068</v>
+        <v>0.6712821165097944</v>
       </c>
       <c r="E22">
-        <v>-0.01138023709094689</v>
+        <v>-0.1399904618122387</v>
       </c>
       <c r="F22">
-        <v>0.8969544476565681</v>
+        <v>0.109384811428725</v>
       </c>
       <c r="G22">
-        <v>0.006263212755671668</v>
+        <v>0.008114739370638913</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>0.5486446257465077</v>
+        <v>-1.02925379462393</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,83 +1191,83 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>0.000894355004784923</v>
+        <v>-0.01137009307998879</v>
       </c>
       <c r="D23">
-        <v>0.6477303485118289</v>
+        <v>1.254597303485119</v>
       </c>
       <c r="E23">
-        <v>0.01468222436223713</v>
+        <v>-0.1017355298326425</v>
       </c>
       <c r="F23">
-        <v>0.8672988340058516</v>
+        <v>0.2457437832378813</v>
       </c>
       <c r="G23">
-        <v>0.005341947237403841</v>
+        <v>0.009751254273632068</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>0.7639964991338688</v>
+        <v>-0.2235147969134239</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
       </c>
       <c r="C24">
-        <v>0.0013352727404877</v>
+        <v>-0.01077020396715132</v>
       </c>
       <c r="D24">
-        <v>0.2018651742559144</v>
+        <v>1.095872297125414</v>
       </c>
       <c r="E24">
-        <v>0.02145085861350314</v>
+        <v>-0.0914025648302748</v>
       </c>
       <c r="F24">
-        <v>0.8071257709678298</v>
+        <v>0.2972581766779891</v>
       </c>
       <c r="G24">
-        <v>0.005458253293397062</v>
+        <v>0.01029134429455607</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>0.3754506305193154</v>
+        <v>-0.3042542186042574</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>32</v>
       </c>
       <c r="C25">
-        <v>0.001634378747683252</v>
+        <v>-0.008792451845618983</v>
       </c>
       <c r="D25">
-        <v>-0.1121732383617401</v>
+        <v>0.2640574917323839</v>
       </c>
       <c r="E25">
-        <v>0.04222785605188627</v>
+        <v>-0.09690029182100117</v>
       </c>
       <c r="F25">
-        <v>0.6306862285209029</v>
+        <v>0.2690234906789499</v>
       </c>
       <c r="G25">
-        <v>0.003391520425583287</v>
+        <v>0.007920720058709746</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>0.1002959988370827</v>
+        <v>-0.8789612481980837</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1278,25 +1278,25 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>0.002008206581851967</v>
+        <v>-0.008313622814055276</v>
       </c>
       <c r="D26">
-        <v>0.06016916815059764</v>
+        <v>0.5530680912405667</v>
       </c>
       <c r="E26">
-        <v>0.04956934270105869</v>
+        <v>-0.09007072969614253</v>
       </c>
       <c r="F26">
-        <v>0.5724555157599729</v>
+        <v>0.3043824594122392</v>
       </c>
       <c r="G26">
-        <v>0.003548863836007602</v>
+        <v>0.008062432959279102</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>0.3212360237913533</v>
+        <v>-0.5277028745866191</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1307,199 +1307,199 @@
         <v>34</v>
       </c>
       <c r="C27">
-        <v>0.002910606543460782</v>
+        <v>-0.008285176995479721</v>
       </c>
       <c r="D27">
-        <v>-0.09101606885440537</v>
+        <v>0.3576809972017301</v>
       </c>
       <c r="E27">
-        <v>0.08898932029334325</v>
+        <v>-0.09327854109276595</v>
       </c>
       <c r="F27">
-        <v>0.3102489173633744</v>
+        <v>0.2874115402288</v>
       </c>
       <c r="G27">
-        <v>0.002857244990995392</v>
+        <v>0.007756230884204579</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>0.2873627817954962</v>
+        <v>-0.7193920122106336</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
         <v>35</v>
       </c>
       <c r="C28">
-        <v>0.003819639793768515</v>
+        <v>-0.007876585197216086</v>
       </c>
       <c r="D28">
-        <v>-0.3000343848045452</v>
+        <v>0.6333463919274149</v>
       </c>
       <c r="E28">
-        <v>0.1074084040434777</v>
+        <v>-0.07343243969542539</v>
       </c>
       <c r="F28">
-        <v>0.2202584472309951</v>
+        <v>0.402715883931969</v>
       </c>
       <c r="G28">
-        <v>0.003100935791908142</v>
+        <v>0.009382190460027345</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>0.1965187883853618</v>
+        <v>-0.3906096837106763</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B29" t="s">
         <v>36</v>
       </c>
       <c r="C29">
-        <v>0.005005186257819178</v>
+        <v>-0.007653034068449995</v>
       </c>
       <c r="D29">
-        <v>0.06328152293733552</v>
+        <v>0.3318782328499958</v>
       </c>
       <c r="E29">
-        <v>0.09960343178241586</v>
+        <v>-0.08271257225602427</v>
       </c>
       <c r="F29">
-        <v>0.2558309040169254</v>
+        <v>0.3457456133182809</v>
       </c>
       <c r="G29">
-        <v>0.00438540011948444</v>
+        <v>0.008087229242644727</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>0.7139557364538287</v>
+        <v>-0.6630161960485035</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B30" t="s">
         <v>37</v>
       </c>
       <c r="C30">
-        <v>0.005036303897916723</v>
+        <v>-0.007116397602228185</v>
       </c>
       <c r="D30">
-        <v>-0.2415441363520735</v>
+        <v>0.3086905791571275</v>
       </c>
       <c r="E30">
-        <v>0.1170089004673201</v>
+        <v>-0.07370352871898217</v>
       </c>
       <c r="F30">
-        <v>0.1815040818700278</v>
+        <v>0.400976692981765</v>
       </c>
       <c r="G30">
-        <v>0.003749106983708376</v>
+        <v>0.008445345909764179</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>0.4131753703771005</v>
+        <v>-0.6164411091325366</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31">
-        <v>0.005375251103513634</v>
+        <v>-0.006547432962187481</v>
       </c>
       <c r="D31">
-        <v>-0.3941656491138812</v>
+        <v>0.5189505638938358</v>
       </c>
       <c r="E31">
-        <v>0.1237749981210166</v>
+        <v>-0.06542913788221089</v>
       </c>
       <c r="F31">
-        <v>0.1573664987895001</v>
+        <v>0.4560462872733495</v>
       </c>
       <c r="G31">
-        <v>0.003779563582768966</v>
+        <v>0.008757831590390291</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>0.3046169943428911</v>
+        <v>-0.3322157211905368</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B32" t="s">
         <v>39</v>
       </c>
       <c r="C32">
-        <v>0.005494836199160802</v>
+        <v>-0.006205416511750781</v>
       </c>
       <c r="D32">
-        <v>0.02365242092766878</v>
+        <v>1.342114983464767</v>
       </c>
       <c r="E32">
-        <v>0.09939927440422713</v>
+        <v>-0.05182409443579528</v>
       </c>
       <c r="F32">
-        <v>0.2568114928987916</v>
+        <v>0.5550919772965187</v>
       </c>
       <c r="G32">
-        <v>0.004824404674834748</v>
+        <v>0.01048777964206642</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.737981126818573</v>
+        <v>0.535410836937166</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33">
-        <v>0.005810896247820698</v>
+        <v>-0.006071784435356049</v>
       </c>
       <c r="D33">
-        <v>-0.6136863393538542</v>
+        <v>0.6003427456966</v>
       </c>
       <c r="E33">
-        <v>0.1342577441512142</v>
+        <v>-0.06179716797315001</v>
       </c>
       <c r="F33">
-        <v>0.1248353568464529</v>
+        <v>0.4814852906569503</v>
       </c>
       <c r="G33">
-        <v>0.003761683772994285</v>
+        <v>0.00860092670443236</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>0.1417301728628366</v>
+        <v>-0.1889892308996864</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1510,112 +1510,112 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>0.006234861432978963</v>
+        <v>-0.004673837804695095</v>
       </c>
       <c r="D34">
-        <v>-0.1968212498940051</v>
+        <v>0.2030741965572799</v>
       </c>
       <c r="E34">
-        <v>0.1423262121928991</v>
+        <v>-0.05075424179698872</v>
       </c>
       <c r="F34">
-        <v>0.1035355656218676</v>
+        <v>0.5632990046204287</v>
       </c>
       <c r="G34">
-        <v>0.003803000462786733</v>
+        <v>0.008066210011179433</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>0.6137107363932601</v>
+        <v>-0.4045247180530825</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
         <v>42</v>
       </c>
       <c r="C35">
-        <v>0.006279536612797869</v>
+        <v>-0.004525807356384819</v>
       </c>
       <c r="D35">
-        <v>0.6527335707623166</v>
+        <v>-0.1327541762062239</v>
       </c>
       <c r="E35">
-        <v>0.08589830043188484</v>
+        <v>-0.04707750890715851</v>
       </c>
       <c r="F35">
-        <v>0.3274212748470318</v>
+        <v>0.5919362058753519</v>
       </c>
       <c r="G35">
-        <v>0.006387974659210947</v>
+        <v>0.00842226918611744</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>1.46907333042604</v>
+        <v>-0.7211091325362503</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
         <v>43</v>
       </c>
       <c r="C36">
-        <v>0.007313044290569099</v>
+        <v>-0.004101902693253497</v>
       </c>
       <c r="D36">
-        <v>-0.6746181209191897</v>
+        <v>0.0606381751886714</v>
       </c>
       <c r="E36">
-        <v>0.1784911958603009</v>
+        <v>-0.04475913289514162</v>
       </c>
       <c r="F36">
-        <v>0.04059166553088651</v>
+        <v>0.6103263103102678</v>
       </c>
       <c r="G36">
-        <v>0.003535729325087568</v>
+        <v>0.00802964875724896</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>0.2760776368547931</v>
+        <v>-0.4726091749342832</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
         <v>44</v>
       </c>
       <c r="C37">
-        <v>0.007951742000050324</v>
+        <v>-0.004087102518443147</v>
       </c>
       <c r="D37">
-        <v>-0.5420375646570001</v>
+        <v>-0.1478889171542438</v>
       </c>
       <c r="E37">
-        <v>0.1934022776545745</v>
+        <v>-0.04379000498589159</v>
       </c>
       <c r="F37">
-        <v>0.02628932811883829</v>
+        <v>0.618087316925219</v>
       </c>
       <c r="G37">
-        <v>0.003537943939015598</v>
+        <v>0.00817809341563124</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>0.491688895349542</v>
+        <v>-0.6792122445518529</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>0.007972270894542588</v>
+        <v>-0.002803290087339951</v>
       </c>
       <c r="D38">
-        <v>-0.3851733655558388</v>
+        <v>0.1224494191469518</v>
       </c>
       <c r="E38">
-        <v>0.1502947210193864</v>
+        <v>-0.02693519075680571</v>
       </c>
       <c r="F38">
-        <v>0.08541135346789273</v>
+        <v>0.7591676015509038</v>
       </c>
       <c r="G38">
-        <v>0.004599444325166711</v>
+        <v>0.009124702445205158</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>0.6512218507346975</v>
+        <v>-0.2419782922072418</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,286 +1655,286 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>0.009222187868944423</v>
+        <v>-0.001791305141902951</v>
       </c>
       <c r="D39">
-        <v>-0.7374893156957519</v>
+        <v>-0.1916999915203937</v>
       </c>
       <c r="E39">
-        <v>0.212031343940811</v>
+        <v>-0.01895933970279453</v>
       </c>
       <c r="F39">
-        <v>0.01465870363541994</v>
+        <v>0.8291640488753816</v>
       </c>
       <c r="G39">
-        <v>0.003727980394087113</v>
+        <v>0.008285078339916466</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>0.4613951072670232</v>
+        <v>-0.4245696599677773</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
       </c>
       <c r="C40">
-        <v>0.009923010949874347</v>
+        <v>-0.001023902054021617</v>
       </c>
       <c r="D40">
-        <v>-0.4685237852963625</v>
+        <v>0.06819333502925469</v>
       </c>
       <c r="E40">
-        <v>0.2063871672803742</v>
+        <v>-0.0107033772436966</v>
       </c>
       <c r="F40">
-        <v>0.0175833910430148</v>
+        <v>0.9030524175326401</v>
       </c>
       <c r="G40">
-        <v>0.004126071974333574</v>
+        <v>0.008389595600046745</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>0.8214676381873027</v>
+        <v>-0.06491393199355554</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.01059110624387908</v>
+        <v>0.0001531403896705352</v>
       </c>
       <c r="D41">
-        <v>-0.3429659967777499</v>
+        <v>-0.2482615110658866</v>
       </c>
       <c r="E41">
-        <v>0.2261035688837395</v>
+        <v>0.001678550111381609</v>
       </c>
       <c r="F41">
-        <v>0.009137276710254116</v>
+        <v>0.9847600068535076</v>
       </c>
       <c r="G41">
-        <v>0.004001909206065623</v>
+        <v>0.008001716285620183</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>1.033877814926531</v>
+        <v>-0.228353260408717</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.01112806367718604</v>
+        <v>0.0005355693403518431</v>
       </c>
       <c r="D42">
-        <v>-0.7748716187568901</v>
+        <v>-0.06640006783685264</v>
       </c>
       <c r="E42">
-        <v>0.2775988390133883</v>
+        <v>0.006022155051520924</v>
       </c>
       <c r="F42">
-        <v>0.001270264642321069</v>
+        <v>0.9453622770513015</v>
       </c>
       <c r="G42">
-        <v>0.003377666390147688</v>
+        <v>0.007799813574075182</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.6717766592772955</v>
+        <v>0.003223946408886971</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.01166321858841574</v>
+        <v>0.0007472229288561029</v>
       </c>
       <c r="D43">
-        <v>-0.6825457474773173</v>
+        <v>-0.1652649877045705</v>
       </c>
       <c r="E43">
-        <v>0.2475000698367658</v>
+        <v>0.007731630497084543</v>
       </c>
       <c r="F43">
-        <v>0.004220835648884702</v>
+        <v>0.9298877206870613</v>
       </c>
       <c r="G43">
-        <v>0.004004468985662376</v>
+        <v>0.00847606819661747</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>0.8336726690167293</v>
+        <v>-0.06812600695327717</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.01208101220411066</v>
+        <v>0.0008360905100157193</v>
       </c>
       <c r="D44">
-        <v>-0.3536662850843724</v>
+        <v>0.08667412872042743</v>
       </c>
       <c r="E44">
-        <v>0.2246145139423911</v>
+        <v>0.009125002122551544</v>
       </c>
       <c r="F44">
-        <v>0.009618451168240904</v>
+        <v>0.9172936957086395</v>
       </c>
       <c r="G44">
-        <v>0.004596765679291696</v>
+        <v>0.00803582669725806</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>1.216865301450013</v>
+        <v>0.1953658950224709</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.01227901306698051</v>
+        <v>0.002886330221970011</v>
       </c>
       <c r="D45">
-        <v>-0.6467133045026716</v>
+        <v>-0.3074742643941322</v>
       </c>
       <c r="E45">
-        <v>0.3121906041268868</v>
+        <v>0.03059615756888783</v>
       </c>
       <c r="F45">
-        <v>0.0002682256781442427</v>
+        <v>0.7276440040989743</v>
       </c>
       <c r="G45">
-        <v>0.003277211507819711</v>
+        <v>0.008269972770853871</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>0.9495583942047952</v>
+        <v>0.06774866446196925</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.01256543223163676</v>
+        <v>0.003298393440698199</v>
       </c>
       <c r="D46">
-        <v>-0.6372278894259307</v>
+        <v>-0.4160530823369796</v>
       </c>
       <c r="E46">
-        <v>0.286128994701209</v>
+        <v>0.0381649491566082</v>
       </c>
       <c r="F46">
-        <v>0.000881260950102316</v>
+        <v>0.6639473648181483</v>
       </c>
       <c r="G46">
-        <v>0.003690591890793931</v>
+        <v>0.007574423341019474</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>0.9962783006868485</v>
+        <v>0.01273806495378632</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.01328801794322019</v>
+        <v>0.003685585321148793</v>
       </c>
       <c r="D47">
-        <v>-0.8206426269821084</v>
+        <v>-0.02018773848893415</v>
       </c>
       <c r="E47">
-        <v>0.3270368449826463</v>
+        <v>0.03722036128895882</v>
       </c>
       <c r="F47">
-        <v>0.0001294904718422685</v>
+        <v>0.6717780543154014</v>
       </c>
       <c r="G47">
-        <v>0.00336766574551233</v>
+        <v>0.00867866998778658</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.9067997056365159</v>
+        <v>0.4589383532604089</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.01359074362422112</v>
+        <v>0.004669120534345672</v>
       </c>
       <c r="D48">
-        <v>-0.8036338081913004</v>
+        <v>-0.4359952514203344</v>
       </c>
       <c r="E48">
-        <v>0.2833264614856008</v>
+        <v>0.05159458602488265</v>
       </c>
       <c r="F48">
-        <v>0.0009949992534448639</v>
+        <v>0.5568477008594102</v>
       </c>
       <c r="G48">
-        <v>0.004034722456957487</v>
+        <v>0.007926481679012413</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>0.9631628629574449</v>
+        <v>0.1709904180446029</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1945,25 +1945,25 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.01621230507387975</v>
+        <v>0.005537780560828131</v>
       </c>
       <c r="D49">
-        <v>-1.164067540066142</v>
+        <v>-0.6358641567031289</v>
       </c>
       <c r="E49">
-        <v>0.4021337784911461</v>
+        <v>0.06079244132551595</v>
       </c>
       <c r="F49">
-        <v>1.756634098639943E-06</v>
+        <v>0.488654972388112</v>
       </c>
       <c r="G49">
-        <v>0.003237421684122149</v>
+        <v>0.007974628854992382</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.943532119538226</v>
+        <v>0.08404731620452821</v>
       </c>
     </row>
   </sheetData>

--- a/output/palmer_drought_trendlines/state/Decade.xlsx
+++ b/output/palmer_drought_trendlines/state/Decade.xlsx
@@ -94,15 +94,15 @@
     <t>Georgia</t>
   </si>
   <si>
+    <t>Texas</t>
+  </si>
+  <si>
     <t>Connecticut</t>
   </si>
   <si>
     <t>Washington</t>
   </si>
   <si>
-    <t>Texas</t>
-  </si>
-  <si>
     <t>Virginia</t>
   </si>
   <si>
@@ -163,10 +163,10 @@
     <t>New Hampshire</t>
   </si>
   <si>
+    <t>Illinois</t>
+  </si>
+  <si>
     <t>New York</t>
-  </si>
-  <si>
-    <t>Illinois</t>
   </si>
   <si>
     <t>Wisconsin</t>
@@ -582,25 +582,25 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>-0.03508872538468063</v>
+        <v>-0.02478121245328064</v>
       </c>
       <c r="D2">
-        <v>1.731814127024507</v>
+        <v>1.2877981853642</v>
       </c>
       <c r="E2">
-        <v>-0.3107506901762977</v>
+        <v>-0.3255925660951496</v>
       </c>
       <c r="F2">
-        <v>0.0002872831800671375</v>
+        <v>0.0001392277406692368</v>
       </c>
       <c r="G2">
-        <v>0.009413086118596127</v>
+        <v>0.006311645505005659</v>
       </c>
       <c r="H2">
         <v>132</v>
       </c>
       <c r="I2">
-        <v>-2.829720172983975</v>
+        <v>-1.933759433562283</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -611,25 +611,25 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>-0.03453208617889363</v>
+        <v>-0.02421189623570698</v>
       </c>
       <c r="D3">
-        <v>1.979958110743663</v>
+        <v>1.535396082421776</v>
       </c>
       <c r="E3">
-        <v>-0.2966509958676844</v>
+        <v>-0.2997637358304585</v>
       </c>
       <c r="F3">
-        <v>0.0005524815337706512</v>
+        <v>0.0004795556607559002</v>
       </c>
       <c r="G3">
-        <v>0.009749948387324566</v>
+        <v>0.006758223379242837</v>
       </c>
       <c r="H3">
         <v>132</v>
       </c>
       <c r="I3">
-        <v>-2.50921309251251</v>
+        <v>-1.612150428220131</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,25 +640,25 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>-0.03357054054230346</v>
+        <v>-0.02347743446242557</v>
       </c>
       <c r="D4">
-        <v>1.867318748410074</v>
+        <v>1.43253879419995</v>
       </c>
       <c r="E4">
-        <v>-0.2781409132969345</v>
+        <v>-0.2772526479717025</v>
       </c>
       <c r="F4">
-        <v>0.001241512086501293</v>
+        <v>0.001288943777741175</v>
       </c>
       <c r="G4">
-        <v>0.01016804276084581</v>
+        <v>0.007135672650071528</v>
       </c>
       <c r="H4">
         <v>132</v>
       </c>
       <c r="I4">
-        <v>-2.496851522089376</v>
+        <v>-1.619527685915374</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -669,25 +669,25 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>-0.03322352764677874</v>
+        <v>-0.02302184020507604</v>
       </c>
       <c r="D5">
-        <v>1.897072670228102</v>
+        <v>1.457615365047063</v>
       </c>
       <c r="E5">
-        <v>-0.2669867485791529</v>
+        <v>-0.253418483657845</v>
       </c>
       <c r="F5">
-        <v>0.001970481768307933</v>
+        <v>0.00336916583147098</v>
       </c>
       <c r="G5">
-        <v>0.01051783395301107</v>
+        <v>0.007707556823280179</v>
       </c>
       <c r="H5">
         <v>132</v>
       </c>
       <c r="I5">
-        <v>-2.421985923853134</v>
+        <v>-1.535223861612823</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -698,25 +698,25 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.03158592907135264</v>
+        <v>-0.02142888675811597</v>
       </c>
       <c r="D6">
-        <v>1.41894021877385</v>
+        <v>0.9814060883575009</v>
       </c>
       <c r="E6">
-        <v>-0.2631578961771068</v>
+        <v>-0.2522559871272376</v>
       </c>
       <c r="F6">
-        <v>0.00229895020729626</v>
+        <v>0.003523096630663403</v>
       </c>
       <c r="G6">
-        <v>0.01015597472652152</v>
+        <v>0.007209571968787284</v>
       </c>
       <c r="H6">
         <v>132</v>
       </c>
       <c r="I6">
-        <v>-2.687230560501993</v>
+        <v>-1.804349190197576</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -727,25 +727,25 @@
         <v>14</v>
       </c>
       <c r="C7">
-        <v>-0.03142366723414805</v>
+        <v>-0.02076064679829626</v>
       </c>
       <c r="D7">
-        <v>1.549571779869416</v>
+        <v>1.090241668786569</v>
       </c>
       <c r="E7">
-        <v>-0.3001135647157354</v>
+        <v>-0.3047649436367897</v>
       </c>
       <c r="F7">
-        <v>0.0004719399738457462</v>
+        <v>0.0003807323421651323</v>
       </c>
       <c r="G7">
-        <v>0.008759997828912363</v>
+        <v>0.005690313123042932</v>
       </c>
       <c r="H7">
         <v>132</v>
       </c>
       <c r="I7">
-        <v>-2.535504960569831</v>
+        <v>-1.608642414991945</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -756,25 +756,25 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-0.02885326236554933</v>
+        <v>-0.01884448597277395</v>
       </c>
       <c r="D8">
-        <v>1.612464004070212</v>
+        <v>1.181316713304503</v>
       </c>
       <c r="E8">
-        <v>-0.2448724933694323</v>
+        <v>-0.23681920833336</v>
       </c>
       <c r="F8">
-        <v>0.004657312747706026</v>
+        <v>0.006257555182885155</v>
       </c>
       <c r="G8">
-        <v>0.01001972555005384</v>
+        <v>0.006780512496615845</v>
       </c>
       <c r="H8">
         <v>132</v>
       </c>
       <c r="I8">
-        <v>-2.138460103451201</v>
+        <v>-1.26846646315611</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -785,25 +785,25 @@
         <v>16</v>
       </c>
       <c r="C9">
-        <v>-0.0273257943108363</v>
+        <v>-0.01643238296512274</v>
       </c>
       <c r="D9">
-        <v>1.80250758924786</v>
+        <v>1.333252946663276</v>
       </c>
       <c r="E9">
-        <v>-0.2555103739107908</v>
+        <v>-0.2237906863191888</v>
       </c>
       <c r="F9">
-        <v>0.003107341937854425</v>
+        <v>0.009894144208798574</v>
       </c>
       <c r="G9">
-        <v>0.009068429046441128</v>
+        <v>0.006276678153341307</v>
       </c>
       <c r="H9">
         <v>132</v>
       </c>
       <c r="I9">
-        <v>-1.749845671160859</v>
+        <v>-0.8029568388026802</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -814,25 +814,25 @@
         <v>17</v>
       </c>
       <c r="C10">
-        <v>-0.02221342126033045</v>
+        <v>-0.01184362561884821</v>
       </c>
       <c r="D10">
-        <v>1.087895700839481</v>
+        <v>0.6411968116679388</v>
       </c>
       <c r="E10">
-        <v>-0.2232554601689635</v>
+        <v>-0.2167284597836472</v>
       </c>
       <c r="F10">
-        <v>0.01007696425709046</v>
+        <v>0.01255745562693217</v>
       </c>
       <c r="G10">
-        <v>0.008506274106862426</v>
+        <v>0.004678967802604728</v>
       </c>
       <c r="H10">
         <v>132</v>
       </c>
       <c r="I10">
-        <v>-1.799849063003477</v>
+        <v>-0.8984745187823288</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -843,25 +843,25 @@
         <v>18</v>
       </c>
       <c r="C11">
-        <v>-0.02066297347187707</v>
+        <v>-0.01011955788636023</v>
       </c>
       <c r="D11">
-        <v>1.057205800050878</v>
+        <v>0.6030278979055377</v>
       </c>
       <c r="E11">
-        <v>-0.2178627853954801</v>
+        <v>-0.2076818982482722</v>
       </c>
       <c r="F11">
-        <v>0.01209140255286077</v>
+        <v>0.01687117949705513</v>
       </c>
       <c r="G11">
-        <v>0.008118555150468637</v>
+        <v>0.004180394673207877</v>
       </c>
       <c r="H11">
         <v>132</v>
       </c>
       <c r="I11">
-        <v>-1.628980751293141</v>
+        <v>-0.7125146273212926</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -872,25 +872,25 @@
         <v>19</v>
       </c>
       <c r="C12">
-        <v>-0.01742679294757647</v>
+        <v>-0.006880070315506595</v>
       </c>
       <c r="D12">
-        <v>0.7239194437378111</v>
+        <v>0.2695990842024932</v>
       </c>
       <c r="E12">
-        <v>-0.1834672648417183</v>
+        <v>-0.1390897691820158</v>
       </c>
       <c r="F12">
-        <v>0.03522708457255905</v>
+        <v>0.1117081463058261</v>
       </c>
       <c r="G12">
-        <v>0.008189400934417949</v>
+        <v>0.004296194396334288</v>
       </c>
       <c r="H12">
         <v>132</v>
       </c>
       <c r="I12">
-        <v>-1.54156363944713</v>
+        <v>-0.6248100568133641</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,25 +901,25 @@
         <v>20</v>
       </c>
       <c r="C13">
-        <v>-0.01729513727178444</v>
+        <v>-0.006751721686267607</v>
       </c>
       <c r="D13">
-        <v>0.627656406342746</v>
+        <v>0.1734785041974055</v>
       </c>
       <c r="E13">
-        <v>-0.1791685741137918</v>
+        <v>-0.1283960604570446</v>
       </c>
       <c r="F13">
-        <v>0.03982341166673574</v>
+        <v>0.1423194907618017</v>
       </c>
       <c r="G13">
-        <v>0.008329241140582491</v>
+        <v>0.004573845916363819</v>
       </c>
       <c r="H13">
         <v>132</v>
       </c>
       <c r="I13">
-        <v>-1.620711438989231</v>
+        <v>-0.7042453150173834</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,25 +930,25 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>-0.01693982610283807</v>
+        <v>-0.00640633165698035</v>
       </c>
       <c r="D14">
-        <v>0.7000193335029263</v>
+        <v>0.2462688035275165</v>
       </c>
       <c r="E14">
-        <v>-0.1795768178720027</v>
+        <v>-0.13370740334289</v>
       </c>
       <c r="F14">
-        <v>0.03936631565967194</v>
+        <v>0.1264029088818864</v>
       </c>
       <c r="G14">
-        <v>0.008138963037474705</v>
+        <v>0.004164521229877923</v>
       </c>
       <c r="H14">
         <v>132</v>
       </c>
       <c r="I14">
-        <v>-1.502158059866023</v>
+        <v>-0.586554311879929</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -959,25 +959,25 @@
         <v>22</v>
       </c>
       <c r="C15">
-        <v>-0.01648034361974836</v>
+        <v>-0.005896692301169533</v>
       </c>
       <c r="D15">
-        <v>0.8478317646061231</v>
+        <v>0.3919206308827271</v>
       </c>
       <c r="E15">
-        <v>-0.1771901715481343</v>
+        <v>-0.1292086138767115</v>
       </c>
       <c r="F15">
-        <v>0.04210208207847842</v>
+        <v>0.139790514574138</v>
       </c>
       <c r="G15">
-        <v>0.008028381600482176</v>
+        <v>0.003969076557902929</v>
       </c>
       <c r="H15">
         <v>132</v>
       </c>
       <c r="I15">
-        <v>-1.294612905961164</v>
+        <v>-0.3746493682693122</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -988,25 +988,25 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>-0.01621008159990608</v>
+        <v>-0.005578478106308176</v>
       </c>
       <c r="D16">
-        <v>0.5675743237513787</v>
+        <v>0.1095975578733148</v>
       </c>
       <c r="E16">
-        <v>-0.1635863279376681</v>
+        <v>-0.09526699115490156</v>
       </c>
       <c r="F16">
-        <v>0.06089818026672635</v>
+        <v>0.2772147012593595</v>
       </c>
       <c r="G16">
-        <v>0.008573859995359425</v>
+        <v>0.005112364674223009</v>
       </c>
       <c r="H16">
         <v>132</v>
       </c>
       <c r="I16">
-        <v>-1.539736284236412</v>
+        <v>-0.6156045959467482</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,25 +1017,25 @@
         <v>24</v>
       </c>
       <c r="C17">
-        <v>-0.01521516936383383</v>
+        <v>-0.004574195905002319</v>
       </c>
       <c r="D17">
-        <v>0.6154857966590352</v>
+        <v>0.1571054015093702</v>
       </c>
       <c r="E17">
-        <v>-0.1605092291234103</v>
+        <v>-0.0901332080318213</v>
       </c>
       <c r="F17">
-        <v>0.06598726241507213</v>
+        <v>0.304045764639766</v>
       </c>
       <c r="G17">
-        <v>0.008206110640579049</v>
+        <v>0.004432889930647427</v>
       </c>
       <c r="H17">
         <v>132</v>
       </c>
       <c r="I17">
-        <v>-1.362486220639363</v>
+        <v>-0.4375400661409312</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1046,112 +1046,112 @@
         <v>25</v>
       </c>
       <c r="C18">
-        <v>-0.01458012771592014</v>
+        <v>-0.003822856453306721</v>
       </c>
       <c r="D18">
-        <v>0.5133806495378619</v>
+        <v>0.04999050284066822</v>
       </c>
       <c r="E18">
-        <v>-0.151535235476888</v>
+        <v>-0.06874381785414072</v>
       </c>
       <c r="F18">
-        <v>0.08283308308976954</v>
+        <v>0.4334970706484574</v>
       </c>
       <c r="G18">
-        <v>0.008341257825409702</v>
+        <v>0.004865797811448551</v>
       </c>
       <c r="H18">
         <v>132</v>
       </c>
       <c r="I18">
-        <v>-1.382035953531757</v>
+        <v>-0.4469808360892055</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19">
-        <v>-0.01394098585210262</v>
+        <v>-0.003295653223228906</v>
       </c>
       <c r="D19">
-        <v>0.5611817179682869</v>
+        <v>-0.08224641736623406</v>
       </c>
       <c r="E19">
-        <v>-0.1536363360892627</v>
+        <v>-0.03854466327465544</v>
       </c>
       <c r="F19">
-        <v>0.07860872593120999</v>
+        <v>0.6608096448749137</v>
       </c>
       <c r="G19">
-        <v>0.007863951692105393</v>
+        <v>0.007493465671556373</v>
       </c>
       <c r="H19">
         <v>132</v>
       </c>
       <c r="I19">
-        <v>-1.251146442805054</v>
+        <v>-0.5106813363859919</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20">
-        <v>-0.01392460847047467</v>
+        <v>-0.003209068613062509</v>
       </c>
       <c r="D20">
-        <v>0.518535402357331</v>
+        <v>0.09888374459425098</v>
       </c>
       <c r="E20">
-        <v>-0.1505977418802818</v>
+        <v>-0.07195638589084863</v>
       </c>
       <c r="F20">
-        <v>0.08477571512489022</v>
+        <v>0.4122637509241347</v>
       </c>
       <c r="G20">
-        <v>0.008016989610981563</v>
+        <v>0.003901312468792748</v>
       </c>
       <c r="H20">
         <v>132</v>
       </c>
       <c r="I20">
-        <v>-1.291663698804376</v>
+        <v>-0.3182951751038752</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
         <v>28</v>
       </c>
       <c r="C21">
-        <v>-0.01376410908687684</v>
+        <v>-0.003176155998669357</v>
       </c>
       <c r="D21">
-        <v>0.3687024506062925</v>
+        <v>0.05552514203340989</v>
       </c>
       <c r="E21">
-        <v>-0.1163552110858013</v>
+        <v>-0.06550972952286026</v>
       </c>
       <c r="F21">
-        <v>0.183972567053515</v>
+        <v>0.4554904151074606</v>
       </c>
       <c r="G21">
-        <v>0.01030458850574281</v>
+        <v>0.004243170121809166</v>
       </c>
       <c r="H21">
         <v>132</v>
       </c>
       <c r="I21">
-        <v>-1.420631730687697</v>
+        <v>-0.3573751377936065</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1162,25 +1162,25 @@
         <v>29</v>
       </c>
       <c r="C22">
-        <v>-0.01308104547025942</v>
+        <v>-0.002429599697343276</v>
       </c>
       <c r="D22">
-        <v>0.6712821165097944</v>
+        <v>0.2124506062918681</v>
       </c>
       <c r="E22">
-        <v>-0.1399904618122387</v>
+        <v>-0.05092923292574382</v>
       </c>
       <c r="F22">
-        <v>0.109384811428725</v>
+        <v>0.5619526696555125</v>
       </c>
       <c r="G22">
-        <v>0.008114739370638913</v>
+        <v>0.004178611048477286</v>
       </c>
       <c r="H22">
         <v>132</v>
       </c>
       <c r="I22">
-        <v>-1.02925379462393</v>
+        <v>-0.1033973543627577</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1191,25 +1191,25 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>-0.01137009307998879</v>
+        <v>-0.0005158151184861937</v>
       </c>
       <c r="D23">
-        <v>1.254597303485119</v>
+        <v>0.7870284066819299</v>
       </c>
       <c r="E23">
-        <v>-0.1017355298326425</v>
+        <v>-0.006553466618561318</v>
       </c>
       <c r="F23">
-        <v>0.2457437832378813</v>
+        <v>0.9405502700563353</v>
       </c>
       <c r="G23">
-        <v>0.009751254273632068</v>
+        <v>0.006903065164725677</v>
       </c>
       <c r="H23">
         <v>132</v>
       </c>
       <c r="I23">
-        <v>-0.2235147969134239</v>
+        <v>0.7199724412787247</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1220,25 +1220,25 @@
         <v>31</v>
       </c>
       <c r="C24">
-        <v>-0.01077020396715132</v>
+        <v>-0.0003315115224807424</v>
       </c>
       <c r="D24">
-        <v>1.095872297125414</v>
+        <v>0.6462055456626812</v>
       </c>
       <c r="E24">
-        <v>-0.0914025648302748</v>
+        <v>-0.00400667940670404</v>
       </c>
       <c r="F24">
-        <v>0.2972581766779891</v>
+        <v>0.9636325841132536</v>
       </c>
       <c r="G24">
-        <v>0.01029134429455607</v>
+        <v>0.007256695032177515</v>
       </c>
       <c r="H24">
         <v>132</v>
       </c>
       <c r="I24">
-        <v>-0.3042542186042574</v>
+        <v>0.6031090477401847</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1249,25 +1249,25 @@
         <v>32</v>
       </c>
       <c r="C25">
-        <v>-0.008792451845618983</v>
+        <v>0.001944425963250692</v>
       </c>
       <c r="D25">
-        <v>0.2640574917323839</v>
+        <v>-0.1984541677266176</v>
       </c>
       <c r="E25">
-        <v>-0.09690029182100117</v>
+        <v>0.04365631741247542</v>
       </c>
       <c r="F25">
-        <v>0.2690234906789499</v>
+        <v>0.6191612590984417</v>
       </c>
       <c r="G25">
-        <v>0.007920720058709746</v>
+        <v>0.003902639057879671</v>
       </c>
       <c r="H25">
         <v>132</v>
       </c>
       <c r="I25">
-        <v>-0.8789612481980837</v>
+        <v>0.0543212074959723</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1278,25 +1278,25 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>-0.008313622814055276</v>
+        <v>0.002490498274726209</v>
       </c>
       <c r="D26">
-        <v>0.5530680912405667</v>
+        <v>0.08765979818536404</v>
       </c>
       <c r="E26">
-        <v>-0.09007072969614253</v>
+        <v>0.05199849353638243</v>
       </c>
       <c r="F26">
-        <v>0.3043824594122392</v>
+        <v>0.5537596264860365</v>
       </c>
       <c r="G26">
-        <v>0.008062432959279102</v>
+        <v>0.004195037814983463</v>
       </c>
       <c r="H26">
         <v>132</v>
       </c>
       <c r="I26">
-        <v>-0.5277028745866191</v>
+        <v>0.4114245738997713</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1307,25 +1307,25 @@
         <v>34</v>
       </c>
       <c r="C27">
-        <v>-0.008285176995479721</v>
+        <v>0.002575163884703445</v>
       </c>
       <c r="D27">
-        <v>0.3576809972017301</v>
+        <v>-0.1101490714830834</v>
       </c>
       <c r="E27">
-        <v>-0.09327854109276595</v>
+        <v>0.06001614966536319</v>
       </c>
       <c r="F27">
-        <v>0.2874115402288</v>
+        <v>0.494233258593154</v>
       </c>
       <c r="G27">
-        <v>0.007756230884204579</v>
+        <v>0.003756483659481777</v>
       </c>
       <c r="H27">
         <v>132</v>
       </c>
       <c r="I27">
-        <v>-0.7193920122106336</v>
+        <v>0.2246222335283644</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1336,25 +1336,25 @@
         <v>35</v>
       </c>
       <c r="C28">
-        <v>-0.007876585197216086</v>
+        <v>0.002968322799052894</v>
       </c>
       <c r="D28">
-        <v>0.6333463919274149</v>
+        <v>0.166181124395828</v>
       </c>
       <c r="E28">
-        <v>-0.07343243969542539</v>
+        <v>0.04068219975725314</v>
       </c>
       <c r="F28">
-        <v>0.402715883931969</v>
+        <v>0.6432574673725571</v>
       </c>
       <c r="G28">
-        <v>0.009382190460027345</v>
+        <v>0.006394039845490092</v>
       </c>
       <c r="H28">
         <v>132</v>
       </c>
       <c r="I28">
-        <v>-0.3906096837106763</v>
+        <v>0.5520630882727042</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1365,25 +1365,25 @@
         <v>36</v>
       </c>
       <c r="C29">
-        <v>-0.007653034068449995</v>
+        <v>0.003164866380969156</v>
       </c>
       <c r="D29">
-        <v>0.3318782328499958</v>
+        <v>-0.1341236326634446</v>
       </c>
       <c r="E29">
-        <v>-0.08271257225602427</v>
+        <v>0.0642987096680654</v>
       </c>
       <c r="F29">
-        <v>0.3457456133182809</v>
+        <v>0.4638829184815968</v>
       </c>
       <c r="G29">
-        <v>0.008087229242644727</v>
+        <v>0.004308060832769522</v>
       </c>
       <c r="H29">
         <v>132</v>
       </c>
       <c r="I29">
-        <v>-0.6630161960485035</v>
+        <v>0.2773089968625457</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1394,25 +1394,25 @@
         <v>37</v>
       </c>
       <c r="C30">
-        <v>-0.007116397602228185</v>
+        <v>0.003558748670984745</v>
       </c>
       <c r="D30">
-        <v>0.3086905791571275</v>
+        <v>-0.1511618756889682</v>
       </c>
       <c r="E30">
-        <v>-0.07370352871898217</v>
+        <v>0.06606113021869126</v>
       </c>
       <c r="F30">
-        <v>0.400976692981765</v>
+        <v>0.4516973166021776</v>
       </c>
       <c r="G30">
-        <v>0.008445345909764179</v>
+        <v>0.004714437927220523</v>
       </c>
       <c r="H30">
         <v>132</v>
       </c>
       <c r="I30">
-        <v>-0.6164411091325366</v>
+        <v>0.3114754515390487</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1423,25 +1423,25 @@
         <v>38</v>
       </c>
       <c r="C31">
-        <v>-0.006547432962187481</v>
+        <v>0.004268813963955152</v>
       </c>
       <c r="D31">
-        <v>0.5189505638938358</v>
+        <v>0.05301992707538367</v>
       </c>
       <c r="E31">
-        <v>-0.06542913788221089</v>
+        <v>0.06939178435382187</v>
       </c>
       <c r="F31">
-        <v>0.4560462872733495</v>
+        <v>0.4291647558237028</v>
       </c>
       <c r="G31">
-        <v>0.008757831590390291</v>
+        <v>0.005382442016756682</v>
       </c>
       <c r="H31">
         <v>132</v>
       </c>
       <c r="I31">
-        <v>-0.3322157211905368</v>
+        <v>0.6079657423895535</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1452,25 +1452,25 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>-0.006205416511750781</v>
+        <v>0.004536973041373961</v>
       </c>
       <c r="D32">
-        <v>1.342114983464767</v>
+        <v>0.8793658950224705</v>
       </c>
       <c r="E32">
-        <v>-0.05182409443579528</v>
+        <v>0.05177140546231467</v>
       </c>
       <c r="F32">
-        <v>0.5550919772965187</v>
+        <v>0.5554948077648503</v>
       </c>
       <c r="G32">
-        <v>0.01048777964206642</v>
+        <v>0.007675766784997461</v>
       </c>
       <c r="H32">
         <v>132</v>
       </c>
       <c r="I32">
-        <v>0.535410836937166</v>
+        <v>1.469172390401086</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1481,25 +1481,25 @@
         <v>40</v>
       </c>
       <c r="C33">
-        <v>-0.006071784435356049</v>
+        <v>0.004774777084189448</v>
       </c>
       <c r="D33">
-        <v>0.6003427456966</v>
+        <v>0.1331062494700246</v>
       </c>
       <c r="E33">
-        <v>-0.06179716797315001</v>
+        <v>0.08133605671188104</v>
       </c>
       <c r="F33">
-        <v>0.4814852906569503</v>
+        <v>0.353859365179697</v>
       </c>
       <c r="G33">
-        <v>0.00860092670443236</v>
+        <v>0.005131649541176746</v>
       </c>
       <c r="H33">
         <v>132</v>
       </c>
       <c r="I33">
-        <v>-0.1889892308996864</v>
+        <v>0.7538272704146528</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1510,25 +1510,25 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>-0.004673837804695095</v>
+        <v>0.006275242157994641</v>
       </c>
       <c r="D34">
-        <v>0.2030741965572799</v>
+        <v>-0.2685784787585858</v>
       </c>
       <c r="E34">
-        <v>-0.05075424179698872</v>
+        <v>0.1234727137324603</v>
       </c>
       <c r="F34">
-        <v>0.5632990046204287</v>
+        <v>0.1583908016372811</v>
       </c>
       <c r="G34">
-        <v>0.008066210011179433</v>
+        <v>0.004423355094935842</v>
       </c>
       <c r="H34">
         <v>132</v>
       </c>
       <c r="I34">
-        <v>-0.4045247180530825</v>
+        <v>0.5472030017807176</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1539,25 +1539,25 @@
         <v>42</v>
       </c>
       <c r="C35">
-        <v>-0.004525807356384819</v>
+        <v>0.006329572953968783</v>
       </c>
       <c r="D35">
-        <v>-0.1327541762062239</v>
+        <v>-0.6003705588060715</v>
       </c>
       <c r="E35">
-        <v>-0.04707750890715851</v>
+        <v>0.1107557216306352</v>
       </c>
       <c r="F35">
-        <v>0.5919362058753519</v>
+        <v>0.2061306105263729</v>
       </c>
       <c r="G35">
-        <v>0.00842226918611744</v>
+        <v>0.004981456954634657</v>
       </c>
       <c r="H35">
         <v>132</v>
       </c>
       <c r="I35">
-        <v>-0.7211091325362503</v>
+        <v>0.2224739252098703</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1568,25 +1568,25 @@
         <v>43</v>
       </c>
       <c r="C36">
-        <v>-0.004101902693253497</v>
+        <v>0.006699462523400455</v>
       </c>
       <c r="D36">
-        <v>0.0606381751886714</v>
+        <v>-0.4046514033748835</v>
       </c>
       <c r="E36">
-        <v>-0.04475913289514162</v>
+        <v>0.1415496589620441</v>
       </c>
       <c r="F36">
-        <v>0.6103263103102678</v>
+        <v>0.1054523224699372</v>
       </c>
       <c r="G36">
-        <v>0.00802964875724896</v>
+        <v>0.004109267861920875</v>
       </c>
       <c r="H36">
         <v>132</v>
       </c>
       <c r="I36">
-        <v>-0.4726091749342832</v>
+        <v>0.4662787246671756</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1597,25 +1597,25 @@
         <v>44</v>
       </c>
       <c r="C37">
-        <v>-0.004087102518443147</v>
+        <v>0.006810167048248965</v>
       </c>
       <c r="D37">
-        <v>-0.1478889171542438</v>
+        <v>-0.617309760027135</v>
       </c>
       <c r="E37">
-        <v>-0.04379000498589159</v>
+        <v>0.1283529137547343</v>
       </c>
       <c r="F37">
-        <v>0.618087316925219</v>
+        <v>0.142454744243781</v>
       </c>
       <c r="G37">
-        <v>0.00817809341563124</v>
+        <v>0.004615015621730932</v>
       </c>
       <c r="H37">
         <v>132</v>
       </c>
       <c r="I37">
-        <v>-0.6792122445518529</v>
+        <v>0.2680119562452303</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1626,25 +1626,25 @@
         <v>45</v>
       </c>
       <c r="C38">
-        <v>-0.002803290087339951</v>
+        <v>0.007810124650216235</v>
       </c>
       <c r="D38">
-        <v>0.1224494191469518</v>
+        <v>-0.3347438310862379</v>
       </c>
       <c r="E38">
-        <v>-0.02693519075680571</v>
+        <v>0.1196473952670885</v>
       </c>
       <c r="F38">
-        <v>0.7591676015509038</v>
+        <v>0.1717872528880028</v>
       </c>
       <c r="G38">
-        <v>0.009124702445205158</v>
+        <v>0.005683972977318342</v>
       </c>
       <c r="H38">
         <v>132</v>
       </c>
       <c r="I38">
-        <v>-0.2419782922072418</v>
+        <v>0.6805723734418727</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1655,25 +1655,25 @@
         <v>46</v>
       </c>
       <c r="C39">
-        <v>-0.001791305141902951</v>
+        <v>0.009061319296323115</v>
       </c>
       <c r="D39">
-        <v>-0.1916999915203937</v>
+        <v>-0.6591976596285934</v>
       </c>
       <c r="E39">
-        <v>-0.01895933970279453</v>
+        <v>0.1681477739974973</v>
       </c>
       <c r="F39">
-        <v>0.8291640488753816</v>
+        <v>0.05394950991865843</v>
       </c>
       <c r="G39">
-        <v>0.008285078339916466</v>
+        <v>0.00465908485200393</v>
       </c>
       <c r="H39">
         <v>132</v>
       </c>
       <c r="I39">
-        <v>-0.4245696599677773</v>
+        <v>0.5187738488934116</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1684,25 +1684,25 @@
         <v>47</v>
       </c>
       <c r="C40">
-        <v>-0.001023902054021617</v>
+        <v>0.009780219034759868</v>
       </c>
       <c r="D40">
-        <v>0.06819333502925469</v>
+        <v>-0.3972149580259478</v>
       </c>
       <c r="E40">
-        <v>-0.0107033772436966</v>
+        <v>0.1807761616835925</v>
       </c>
       <c r="F40">
-        <v>0.9030524175326401</v>
+        <v>0.0380488468981717</v>
       </c>
       <c r="G40">
-        <v>0.008389595600046745</v>
+        <v>0.004666817556490344</v>
       </c>
       <c r="H40">
         <v>132</v>
       </c>
       <c r="I40">
-        <v>-0.06491393199355554</v>
+        <v>0.8742135164928352</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1713,83 +1713,83 @@
         <v>48</v>
       </c>
       <c r="C41">
-        <v>0.0001531403896705352</v>
+        <v>0.01095891500172854</v>
       </c>
       <c r="D41">
-        <v>-0.2482615110658866</v>
+        <v>-0.7137410328160776</v>
       </c>
       <c r="E41">
-        <v>0.001678550111381609</v>
+        <v>0.2345379418539186</v>
       </c>
       <c r="F41">
-        <v>0.9847600068535076</v>
+        <v>0.006792062442384172</v>
       </c>
       <c r="G41">
-        <v>0.008001716285620183</v>
+        <v>0.003983793585204906</v>
       </c>
       <c r="H41">
         <v>132</v>
       </c>
       <c r="I41">
-        <v>-0.228353260408717</v>
+        <v>0.7109179174086326</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42">
-        <v>0.0005355693403518431</v>
+        <v>0.01161803612312389</v>
       </c>
       <c r="D42">
-        <v>-0.06640006783685264</v>
+        <v>-0.6335461714576449</v>
       </c>
       <c r="E42">
-        <v>0.006022155051520924</v>
+        <v>0.2026066031674695</v>
       </c>
       <c r="F42">
-        <v>0.9453622770513015</v>
+        <v>0.01981404804540988</v>
       </c>
       <c r="G42">
-        <v>0.007799813574075182</v>
+        <v>0.004924992352542051</v>
       </c>
       <c r="H42">
         <v>132</v>
       </c>
       <c r="I42">
-        <v>0.003223946408886971</v>
+        <v>0.8767985245484613</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B43" t="s">
         <v>50</v>
       </c>
       <c r="C43">
-        <v>0.0007472229288561029</v>
+        <v>0.01162574995597128</v>
       </c>
       <c r="D43">
-        <v>-0.1652649877045705</v>
+        <v>-0.5441309251250745</v>
       </c>
       <c r="E43">
-        <v>0.007731630497084543</v>
+        <v>0.2435150804388149</v>
       </c>
       <c r="F43">
-        <v>0.9298877206870613</v>
+        <v>0.004898260773525278</v>
       </c>
       <c r="G43">
-        <v>0.00847606819661747</v>
+        <v>0.004061150705588164</v>
       </c>
       <c r="H43">
         <v>132</v>
       </c>
       <c r="I43">
-        <v>-0.06812600695327717</v>
+        <v>0.9672165691511918</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1800,25 +1800,25 @@
         <v>51</v>
       </c>
       <c r="C44">
-        <v>0.0008360905100157193</v>
+        <v>0.01196375098656961</v>
       </c>
       <c r="D44">
-        <v>0.08667412872042743</v>
+        <v>-0.392671245654202</v>
       </c>
       <c r="E44">
-        <v>0.009125002122551544</v>
+        <v>0.2267125442885684</v>
       </c>
       <c r="F44">
-        <v>0.9172936957086395</v>
+        <v>0.00894669321573684</v>
       </c>
       <c r="G44">
-        <v>0.00803582669725806</v>
+        <v>0.004507772852864634</v>
       </c>
       <c r="H44">
         <v>132</v>
       </c>
       <c r="I44">
-        <v>0.1953658950224709</v>
+        <v>1.162616382599848</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1829,25 +1829,25 @@
         <v>52</v>
       </c>
       <c r="C45">
-        <v>0.002886330221970011</v>
+        <v>0.01380840263780992</v>
       </c>
       <c r="D45">
-        <v>-0.3074742643941322</v>
+        <v>-0.7779635376918517</v>
       </c>
       <c r="E45">
-        <v>0.03059615756888783</v>
+        <v>0.2541833916731382</v>
       </c>
       <c r="F45">
-        <v>0.7276440040989743</v>
+        <v>0.003271210651591114</v>
       </c>
       <c r="G45">
-        <v>0.008269972770853871</v>
+        <v>0.004608092024232644</v>
       </c>
       <c r="H45">
         <v>132</v>
       </c>
       <c r="I45">
-        <v>0.06774866446196925</v>
+        <v>1.017128805223438</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1858,25 +1858,25 @@
         <v>53</v>
       </c>
       <c r="C46">
-        <v>0.003298393440698199</v>
+        <v>0.01458093393081947</v>
       </c>
       <c r="D46">
-        <v>-0.4160530823369796</v>
+        <v>-0.9020702111422036</v>
       </c>
       <c r="E46">
-        <v>0.0381649491566082</v>
+        <v>0.303210168042806</v>
       </c>
       <c r="F46">
-        <v>0.6639473648181483</v>
+        <v>0.0004092298013119275</v>
       </c>
       <c r="G46">
-        <v>0.007574423341019474</v>
+        <v>0.004019092826967437</v>
       </c>
       <c r="H46">
         <v>132</v>
       </c>
       <c r="I46">
-        <v>0.01273806495378632</v>
+        <v>0.993451199864327</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1887,25 +1887,25 @@
         <v>54</v>
       </c>
       <c r="C47">
-        <v>0.003685585321148793</v>
+        <v>0.01474875838991841</v>
       </c>
       <c r="D47">
-        <v>-0.02018773848893415</v>
+        <v>-0.4967551937590101</v>
       </c>
       <c r="E47">
-        <v>0.03722036128895882</v>
+        <v>0.2323097468917533</v>
       </c>
       <c r="F47">
-        <v>0.6717780543154014</v>
+        <v>0.007352897633519464</v>
       </c>
       <c r="G47">
-        <v>0.00867866998778658</v>
+        <v>0.005415883434434139</v>
       </c>
       <c r="H47">
         <v>132</v>
       </c>
       <c r="I47">
-        <v>0.4589383532604089</v>
+        <v>1.420583396930383</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1916,25 +1916,25 @@
         <v>55</v>
       </c>
       <c r="C48">
-        <v>0.004669120534345672</v>
+        <v>0.01588827596553367</v>
       </c>
       <c r="D48">
-        <v>-0.4359952514203344</v>
+        <v>-0.9192819469176636</v>
       </c>
       <c r="E48">
-        <v>0.05159458602488265</v>
+        <v>0.2966056393024872</v>
       </c>
       <c r="F48">
-        <v>0.5568477008594102</v>
+        <v>0.000553615868472945</v>
       </c>
       <c r="G48">
-        <v>0.007926481679012413</v>
+        <v>0.004486721249738871</v>
       </c>
       <c r="H48">
         <v>132</v>
       </c>
       <c r="I48">
-        <v>0.1709904180446029</v>
+        <v>1.146193928601713</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1945,25 +1945,25 @@
         <v>56</v>
       </c>
       <c r="C49">
-        <v>0.005537780560828131</v>
+        <v>0.01648134877926281</v>
       </c>
       <c r="D49">
-        <v>-0.6358641567031289</v>
+        <v>-1.1072794030357</v>
       </c>
       <c r="E49">
-        <v>0.06079244132551595</v>
+        <v>0.3332445341820956</v>
       </c>
       <c r="F49">
-        <v>0.488654972388112</v>
+        <v>9.442786256192025E-05</v>
       </c>
       <c r="G49">
-        <v>0.007974628854992382</v>
+        <v>0.004089745066683646</v>
       </c>
       <c r="H49">
         <v>132</v>
       </c>
       <c r="I49">
-        <v>0.08404731620452821</v>
+        <v>1.035295938268465</v>
       </c>
     </row>
   </sheetData>
